--- a/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/501155606.xlsx
+++ b/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/501155606.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Copper cable</t>
+          <t>Copper products</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Copper cable</t>
+          <t>Copper products</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Copper cable</t>
+          <t>Copper products</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Copper cable</t>
+          <t>Copper products</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Copper cable</t>
+          <t>Copper products</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Copper cable</t>
+          <t>Copper products</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Copper cable</t>
+          <t>Copper products</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>85389000</t>
+          <t>85369000</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -3315,7 +3315,7 @@
       <c r="AJ32" s="2" t="n"/>
       <c r="AK32" s="2" t="inlineStr">
         <is>
-          <t>85389000</t>
+          <t>85369000</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>85362000</t>
+          <t>85369000</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -3647,7 +3647,7 @@
       <c r="AJ36" s="2" t="n"/>
       <c r="AK36" s="2" t="inlineStr">
         <is>
-          <t>85362000</t>
+          <t>85369000</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Electrical connectors</t>
+          <t>Electrical equipment</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
